--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_56_R6.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_56_R6.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3425</v>
+        <v>4.3398</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3067</v>
+        <v>2.6736</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0359</v>
+        <v>1.6662</v>
       </c>
       <c r="G2" t="n">
         <v>2.5377</v>
@@ -610,13 +610,13 @@
         <v>3.0154</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3772</v>
+        <v>0.3745</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3293</v>
+        <v>0.6963</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0479</v>
+        <v>-0.3218</v>
       </c>
       <c r="V2" t="n">
         <v>-1.3558</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0631</v>
+        <v>3.9418</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7784</v>
+        <v>1.7915</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2848</v>
+        <v>2.1503</v>
       </c>
       <c r="G3" t="n">
         <v>2.9102</v>
@@ -688,13 +688,13 @@
         <v>2.0876</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3179</v>
+        <v>0.1966</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9189</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.601</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>-0.7886</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.07</v>
+        <v>3.7253</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9812</v>
+        <v>3.2668</v>
       </c>
       <c r="F4" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.4585</v>
       </c>
       <c r="G4" t="n">
         <v>0.4542</v>
@@ -766,13 +766,13 @@
         <v>3.0154</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.2813</v>
+        <v>-0.626</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.4857</v>
+        <v>-0.2001</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7956</v>
+        <v>-0.4259</v>
       </c>
       <c r="V4" t="n">
         <v>4.8249</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0047</v>
+        <v>3.2651</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7254</v>
+        <v>2.5825</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2793</v>
+        <v>0.6826</v>
       </c>
       <c r="G5" t="n">
         <v>3.4026</v>
@@ -844,13 +844,13 @@
         <v>3.0154</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.6298</v>
+        <v>-0.3695</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6994</v>
+        <v>0.1577</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9304</v>
+        <v>-0.5272</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2743</v>
+        <v>0.0212</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5153</v>
+        <v>0.1615</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2411</v>
+        <v>-0.1402</v>
       </c>
       <c r="G6" t="n">
         <v>0.2427</v>
@@ -922,13 +922,13 @@
         <v>1.6237</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2482</v>
+        <v>-0.0048</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9085</v>
+        <v>0.5546</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6603</v>
+        <v>-0.5594</v>
       </c>
       <c r="V6" t="n">
         <v>-1.6083</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. MASSA</t>
+          <t>Z. SELJAAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6365</v>
+        <v>-0.5723</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7255</v>
+        <v>-0.2985</v>
       </c>
       <c r="F7" t="n">
-        <v>0.089</v>
+        <v>-0.2738</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4301</v>
+        <v>-0.5829</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5606</v>
+        <v>-1.1415</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1305</v>
+        <v>0.5586</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1707</v>
+        <v>-0.2319</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0133</v>
+        <v>-0.215</v>
       </c>
       <c r="L7" t="n">
-        <v>0.184</v>
+        <v>-0.017</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6008</v>
+        <v>-0.3509</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5473</v>
+        <v>-0.9265</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0535</v>
+        <v>0.5756</v>
       </c>
       <c r="P7" t="n">
+        <v>1.8556</v>
+      </c>
+      <c r="Q7" t="n">
         <v>-0.232</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-1.1598</v>
-      </c>
       <c r="R7" t="n">
-        <v>0.9278</v>
+        <v>2.0876</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8452</v>
+        <v>-0.2368</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2636</v>
+        <v>0.1654</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5816</v>
+        <v>-0.4022</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.8197</v>
+        <v>-1.6083</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8197</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Z. SELJAAS</t>
+          <t>B. MASSA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0152</v>
+        <v>-1.2517</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6405</v>
+        <v>-1.0046</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3747</v>
+        <v>-0.2471</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5829</v>
+        <v>-0.4301</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1415</v>
+        <v>-0.5606</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5586</v>
+        <v>0.1305</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2319</v>
+        <v>0.1707</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.215</v>
+        <v>-0.0133</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.017</v>
+        <v>0.184</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3509</v>
+        <v>-0.6008</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9265</v>
+        <v>-0.5473</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5756</v>
+        <v>-0.0535</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8556</v>
+        <v>-0.232</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0876</v>
+        <v>0.9278</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6796</v>
+        <v>0.23</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1766</v>
+        <v>-0.0156</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.503</v>
+        <v>0.2456</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.6083</v>
+        <v>-0.8197</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.6083</v>
+        <v>-0.8197</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. ATAMNA</t>
+          <t>M. AJINCA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6263</v>
+        <v>-1.6123</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9233</v>
+        <v>-2.3654</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2971</v>
+        <v>0.7531</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.8835</v>
+        <v>-2.3484</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.0432</v>
+        <v>-2.2747</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.8404</v>
+        <v>-0.0737</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.4189</v>
+        <v>-1.4722</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6855</v>
+        <v>-1.5055</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.7334</v>
+        <v>0.0333</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4647</v>
+        <v>-0.8762</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3577</v>
+        <v>-0.7692</v>
       </c>
       <c r="O9" t="n">
         <v>-0.107</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4639</v>
+        <v>1.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7934</v>
+        <v>-0.3361</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4955</v>
+        <v>-0.5737</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2978</v>
+        <v>0.2377</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. AJINCA</t>
+          <t>A. ATAMNA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5098</v>
+        <v>-1.9459</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0613</v>
+        <v>-2.0413</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5515</v>
+        <v>0.0954</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.3484</v>
+        <v>-2.8835</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.2747</v>
+        <v>-1.0432</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0737</v>
+        <v>-1.8404</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.4722</v>
+        <v>-2.4189</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.5055</v>
+        <v>-0.6855</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0333</v>
+        <v>-1.7334</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8762</v>
+        <v>-0.4647</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7692</v>
+        <v>-0.3577</v>
       </c>
       <c r="O10" t="n">
         <v>-0.107</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.4639</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2336</v>
+        <v>0.4738</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2696</v>
+        <v>0.3776</v>
       </c>
       <c r="U10" t="n">
-        <v>0.036</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6586</v>
+        <v>-2.6176</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1951</v>
+        <v>-2.1205</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4635</v>
+        <v>-0.4971</v>
       </c>
       <c r="G11" t="n">
         <v>-0.7086</v>
@@ -1312,13 +1312,13 @@
         <v>0.4639</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6067</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1968</v>
+        <v>0.2715</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4099</v>
+        <v>0.3763</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8608</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.7366</v>
+        <v>-4.6016</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.413</v>
+        <v>-4.1771</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3237</v>
+        <v>-0.4245</v>
       </c>
       <c r="G12" t="n">
         <v>-2.9761</v>
@@ -1390,13 +1390,13 @@
         <v>0.4639</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0075</v>
+        <v>0.1426</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1415</v>
+        <v>0.0944</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1489</v>
+        <v>0.0481</v>
       </c>
       <c r="V12" t="n">
         <v>-1.0722</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.571599999999999</v>
+        <v>2.6918</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.6517</v>
+        <v>-1.5315</v>
       </c>
       <c r="F13" t="n">
-        <v>4.2235</v>
+        <v>4.2234</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.3822000000000001</v>
+        <v>-0.3821999999999997</v>
       </c>
       <c r="H13" t="n">
         <v>-9.867599999999999</v>
@@ -1444,7 +1444,7 @@
         <v>1.0875</v>
       </c>
       <c r="K13" t="n">
-        <v>-6.322400000000001</v>
+        <v>-6.322400000000002</v>
       </c>
       <c r="L13" t="n">
         <v>7.4098</v>
@@ -1468,16 +1468,16 @@
         <v>18.5563</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6282</v>
+        <v>0.4919999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>1.339799999999999</v>
+        <v>2.4601</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.9682</v>
+        <v>-1.968</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.216599999999999</v>
+        <v>-3.2166</v>
       </c>
       <c r="W13" t="n">
         <v>7.678299999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.3576</v>
+        <v>4.5649</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7729</v>
+        <v>3.655</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5847</v>
+        <v>0.91</v>
       </c>
       <c r="G14" t="n">
         <v>1.707</v>
@@ -1546,13 +1546,13 @@
         <v>1.3917</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4187</v>
+        <v>0.626</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5113</v>
+        <v>0.3934</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0927</v>
+        <v>0.2326</v>
       </c>
       <c r="V14" t="n">
         <v>1.0722</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. PETRUSEV</t>
+          <t>M. KABENGELE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.8979</v>
+        <v>3.3667</v>
       </c>
       <c r="E15" t="n">
-        <v>3.8831</v>
+        <v>0.7299</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0149</v>
+        <v>2.6368</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4848</v>
+        <v>0.2031</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9002</v>
+        <v>2.8664</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.385</v>
+        <v>-2.6633</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0435</v>
+        <v>0.1954</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.1037</v>
+        <v>1.6944</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1472</v>
+        <v>-1.4991</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5284</v>
+        <v>0.0077</v>
       </c>
       <c r="N15" t="n">
-        <v>1.0039</v>
+        <v>1.1719</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.5322</v>
+        <v>-1.1642</v>
       </c>
       <c r="P15" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-1.3917</v>
+      </c>
+      <c r="R15" t="n">
         <v>1.6237</v>
       </c>
-      <c r="Q15" t="n">
-        <v>-0.232</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.8556</v>
-      </c>
       <c r="S15" t="n">
-        <v>2.6174</v>
+        <v>0.7872</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7853</v>
+        <v>0.5704</v>
       </c>
       <c r="U15" t="n">
-        <v>0.832</v>
+        <v>0.2168</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1418</v>
+        <v>2.1444</v>
       </c>
       <c r="W15" t="n">
-        <v>2.2862</v>
+        <v>1.3558</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.1444</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. KABENGELE</t>
+          <t>F. PETRUSEV</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.2608</v>
+        <v>2.5739</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0837</v>
+        <v>2.9395</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1771</v>
+        <v>-0.3656</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2031</v>
+        <v>-0.4848</v>
       </c>
       <c r="H16" t="n">
-        <v>2.8664</v>
+        <v>0.9002</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.6633</v>
+        <v>-1.385</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1954</v>
+        <v>0.0435</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6944</v>
+        <v>-0.1037</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.4991</v>
+        <v>0.1472</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0077</v>
+        <v>-0.5284</v>
       </c>
       <c r="N16" t="n">
-        <v>1.1719</v>
+        <v>1.0039</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.1642</v>
+        <v>-1.5322</v>
       </c>
       <c r="P16" t="n">
-        <v>0.232</v>
+        <v>1.6237</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6814</v>
+        <v>1.2933</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9243</v>
+        <v>0.8417</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2429</v>
+        <v>0.4516</v>
       </c>
       <c r="V16" t="n">
-        <v>2.1444</v>
+        <v>0.1418</v>
       </c>
       <c r="W16" t="n">
-        <v>1.3558</v>
+        <v>2.2862</v>
       </c>
       <c r="X16" t="n">
-        <v>0.7886</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. ARMSTRONG</t>
+          <t>K. KONDIC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3396</v>
+        <v>0.632</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2214</v>
+        <v>1.127</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5610000000000001</v>
+        <v>-0.495</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4367</v>
+        <v>1.7301</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4166</v>
+        <v>1.0242</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0201</v>
+        <v>0.706</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3761</v>
+        <v>1.3478</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3025</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0736</v>
+        <v>0.7092000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0606</v>
+        <v>0.3823</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1141</v>
+        <v>0.3856</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0535</v>
+        <v>-0.0033</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6959</v>
+        <v>-0.232</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5988</v>
+        <v>-0.4718</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5623</v>
+        <v>-0.275</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0365</v>
+        <v>-0.1968</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="18">
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2326</v>
+        <v>0.4685</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2147</v>
+        <v>0.0212</v>
       </c>
       <c r="F18" t="n">
         <v>0.4473</v>
@@ -1858,10 +1858,10 @@
         <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2399</v>
+        <v>-0.004</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2987</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="U18" t="n">
         <v>0.0589</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. KONDIC</t>
+          <t>T. ARMSTRONG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.003</v>
+        <v>0.0701</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6552</v>
+        <v>-0.4573</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6523</v>
+        <v>0.5274</v>
       </c>
       <c r="G19" t="n">
-        <v>1.7301</v>
+        <v>0.4367</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0242</v>
+        <v>0.4166</v>
       </c>
       <c r="I19" t="n">
-        <v>0.706</v>
+        <v>0.0201</v>
       </c>
       <c r="J19" t="n">
-        <v>1.3478</v>
+        <v>0.3761</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6385999999999999</v>
+        <v>0.3025</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7092000000000001</v>
+        <v>0.0736</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3823</v>
+        <v>0.0606</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3856</v>
+        <v>0.1141</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0033</v>
+        <v>-0.0535</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.232</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1009</v>
+        <v>0.3293</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7468</v>
+        <v>0.3264</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3541</v>
+        <v>0.0029</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. ABASS</t>
+          <t>D. BACON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0624</v>
+        <v>-0.1527</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-2.904</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4623</v>
+        <v>2.7513</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0882</v>
+        <v>-2.0203</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0815</v>
+        <v>0.3754</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0067</v>
+        <v>-2.3957</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.6493</v>
+        <v>-1.4811</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.4887</v>
+        <v>-0.6177</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.1607</v>
+        <v>-0.8635</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5611</v>
+        <v>-0.5392</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4071</v>
+        <v>0.9931</v>
       </c>
       <c r="O20" t="n">
-        <v>0.154</v>
+        <v>-1.5322</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9278</v>
+        <v>-3.7112</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-6.0307</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9278</v>
+        <v>2.3195</v>
       </c>
       <c r="S20" t="n">
-        <v>0.098</v>
+        <v>0.3596</v>
       </c>
       <c r="T20" t="n">
-        <v>1.1246</v>
+        <v>0.1772</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.0266</v>
+        <v>0.1823</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>5.2192</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>4.4306</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. BACON</t>
+          <t>A. ABASS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9340000000000001</v>
+        <v>-0.3776</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.7297</v>
+        <v>-1.2324</v>
       </c>
       <c r="F21" t="n">
-        <v>2.7957</v>
+        <v>0.8548</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.0203</v>
+        <v>-1.0882</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3754</v>
+        <v>-1.0815</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.3957</v>
+        <v>-0.0067</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.4811</v>
+        <v>-1.6493</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6177</v>
+        <v>-1.4887</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.8635</v>
+        <v>-0.1607</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5392</v>
+        <v>0.5611</v>
       </c>
       <c r="N21" t="n">
-        <v>0.9931</v>
+        <v>0.4071</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.5322</v>
+        <v>0.154</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.7112</v>
+        <v>0.9278</v>
       </c>
       <c r="Q21" t="n">
-        <v>-6.0307</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.3195</v>
+        <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4217</v>
+        <v>-0.2172</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6484</v>
+        <v>0.4169</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2267</v>
+        <v>-0.6341</v>
       </c>
       <c r="V21" t="n">
-        <v>5.2192</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>4.4306</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.7886</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.5847</v>
+        <v>-4.6804</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.9599</v>
+        <v>-3.3702</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6248</v>
+        <v>-1.3102</v>
       </c>
       <c r="G22" t="n">
         <v>1.5244</v>
@@ -2170,13 +2170,13 @@
         <v>1.6237</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5034</v>
+        <v>0.4009</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6484</v>
+        <v>-0.0587</v>
       </c>
       <c r="U22" t="n">
-        <v>0.145</v>
+        <v>0.4595</v>
       </c>
       <c r="V22" t="n">
         <v>-3.3584</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.0821</v>
+        <v>-6.4644</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.5041</v>
+        <v>-5.2682</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.578</v>
+        <v>-1.1962</v>
       </c>
       <c r="G23" t="n">
         <v>-1.4023</v>
@@ -2248,13 +2248,13 @@
         <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.52</v>
+        <v>-0.9023</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5975</v>
+        <v>-0.3615</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9225</v>
+        <v>-0.5407999999999999</v>
       </c>
       <c r="V23" t="n">
         <v>-1.6083</v>
@@ -2281,22 +2281,22 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.571699999999999</v>
+        <v>0.0009999999999994458</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.7596</v>
+        <v>-4.759500000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>3.1879</v>
+        <v>4.7606</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3822999999999994</v>
+        <v>0.3822999999999996</v>
       </c>
       <c r="H24" t="n">
         <v>9.867499999999998</v>
       </c>
       <c r="I24" t="n">
-        <v>-9.485200000000001</v>
+        <v>-9.485199999999999</v>
       </c>
       <c r="J24" t="n">
         <v>1.4697</v>
@@ -2311,13 +2311,13 @@
         <v>-1.0876</v>
       </c>
       <c r="N24" t="n">
-        <v>6.3225</v>
+        <v>6.322499999999999</v>
       </c>
       <c r="O24" t="n">
         <v>-7.4099</v>
       </c>
       <c r="P24" t="n">
-        <v>-5.798699999999999</v>
+        <v>-5.7987</v>
       </c>
       <c r="Q24" t="n">
         <v>-18.5563</v>
@@ -2326,13 +2326,13 @@
         <v>12.7574</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6284000000000001</v>
+        <v>2.201</v>
       </c>
       <c r="T24" t="n">
         <v>1.968</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.3397</v>
+        <v>0.2329000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>3.2166</v>
